--- a/Document/Design/属性表.xlsx
+++ b/Document/Design/属性表.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Vital" sheetId="1" r:id="rId1"/>
     <sheet name="Core" sheetId="2" r:id="rId2"/>
     <sheet name="Resource" sheetId="3" r:id="rId3"/>
+    <sheet name="Combat" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
   <si>
     <t>百分比 P
 数值 V
@@ -82,7 +83,7 @@
     <t>生命值每秒增加的数量</t>
   </si>
   <si>
-    <t>生命值消耗率</t>
+    <t>生命消耗率</t>
   </si>
   <si>
     <t>HealthConsumeRate</t>
@@ -91,7 +92,7 @@
     <t>生命值每秒消耗的数量</t>
   </si>
   <si>
-    <t>生命值变化率</t>
+    <t>生命变化率</t>
   </si>
   <si>
     <t>HealthNetFlow</t>
@@ -110,6 +111,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>防具提供的承伤属性，</t>
     </r>
     <r>
@@ -244,6 +252,69 @@
   </si>
   <si>
     <t>质能转换率</t>
+  </si>
+  <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>最大能量</t>
+  </si>
+  <si>
+    <t>MaxEnergy</t>
+  </si>
+  <si>
+    <t>能量回复率</t>
+  </si>
+  <si>
+    <t>EnergyRegenRate</t>
+  </si>
+  <si>
+    <t>能量消耗率</t>
+  </si>
+  <si>
+    <t>EnergyConsumeRate</t>
+  </si>
+  <si>
+    <t>能量变化率</t>
+  </si>
+  <si>
+    <t>EnergyNetFlow</t>
+  </si>
+  <si>
+    <t>物质</t>
+  </si>
+  <si>
+    <t>物质量</t>
+  </si>
+  <si>
+    <t>Matter</t>
+  </si>
+  <si>
+    <t>最大物质量</t>
+  </si>
+  <si>
+    <t>MaxMatter</t>
+  </si>
+  <si>
+    <t>物质回复率</t>
+  </si>
+  <si>
+    <t>MatterRegenRate</t>
+  </si>
+  <si>
+    <t>物质消耗率</t>
+  </si>
+  <si>
+    <t>MatterConsumeRate</t>
+  </si>
+  <si>
+    <t>物质变化率</t>
+  </si>
+  <si>
+    <t>MatterNetFlow</t>
   </si>
 </sst>
 </file>
@@ -878,14 +949,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1204,187 +1275,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="15.5555555555556" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="15.5555555555556" defaultRowHeight="24" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="15.5555555555556" style="2"/>
-    <col min="2" max="2" width="19.2222222222222" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13" style="2" customWidth="1"/>
-    <col min="5" max="5" width="56.5555555555556" style="2" customWidth="1"/>
-    <col min="6" max="6" width="45.2222222222222" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="15.5555555555556" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.5555555555556" style="1"/>
+    <col min="2" max="2" width="19.2222222222222" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" customWidth="1"/>
+    <col min="5" max="5" width="56.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.2222222222222" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="15.5555555555556" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="56" customHeight="1" spans="1:6">
-      <c r="D1" s="3" t="s">
+    <row r="1" ht="56" customHeight="1" spans="1:5">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="B2" s="4" t="s">
+    <row r="2" s="3" customFormat="1" customHeight="1" spans="1:5">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:6">
-      <c r="A3" s="4" t="s">
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:6">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+    <row r="4" customHeight="1" spans="1:5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:6">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+    <row r="5" customHeight="1" spans="1:5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" customHeight="1" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1" spans="1:6">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="40" customHeight="1" spans="1:5">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:6">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
+    <row r="9" customHeight="1" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
+    <row r="10" customHeight="1" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:6">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2" t="s">
+    <row r="11" customHeight="1" spans="1:5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:6">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
+    <row r="12" customHeight="1" spans="1:5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1407,134 +1476,133 @@
   <dimension ref="B1:F8"/>
   <sheetFormatPr defaultColWidth="15.6666666666667" defaultRowHeight="24" customHeight="1" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="15.6666666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.7777777777778" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.7777777777778" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.5555555555556" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="15.6666666666667" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="52.7777777777778" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="15.6666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:6">
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="2:6">
-      <c r="B2" s="4" t="s">
+    <row r="2" s="3" customFormat="1" customHeight="1" spans="2:6">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" ht="49" customHeight="1" spans="2:6">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="49" customHeight="1" spans="2:6">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" ht="49" customHeight="1" spans="2:6">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1" spans="2:6">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" ht="49" customHeight="1" spans="2:6">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" ht="49" customHeight="1" spans="2:6">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1552,11 +1620,183 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="14.6666666666667" defaultRowHeight="35" customHeight="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="2" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="49.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.2222222222222" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="14.6666666666667" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="68" customHeight="1" spans="1:6">
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:6">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" spans="1:6">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1" spans="1:6">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:6">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1" spans="1:6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Document/Design/属性表.xlsx
+++ b/Document/Design/属性表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Vital" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="127">
   <si>
     <t>百分比 P
 数值 V
@@ -260,30 +260,45 @@
     <t>Energy</t>
   </si>
   <si>
+    <t>使用装备时主要消耗的资源</t>
+  </si>
+  <si>
     <t>最大能量</t>
   </si>
   <si>
     <t>MaxEnergy</t>
   </si>
   <si>
+    <t>能量的上限</t>
+  </si>
+  <si>
     <t>能量回复率</t>
   </si>
   <si>
     <t>EnergyRegenRate</t>
   </si>
   <si>
+    <t>能量每秒回复的数量</t>
+  </si>
+  <si>
     <t>能量消耗率</t>
   </si>
   <si>
     <t>EnergyConsumeRate</t>
   </si>
   <si>
+    <t>能量每秒消耗的数量</t>
+  </si>
+  <si>
     <t>能量变化率</t>
   </si>
   <si>
     <t>EnergyNetFlow</t>
   </si>
   <si>
+    <t>能量每秒变化的数量</t>
+  </si>
+  <si>
     <t>物质</t>
   </si>
   <si>
@@ -293,28 +308,142 @@
     <t>Matter</t>
   </si>
   <si>
+    <t>制作道具、部分装备时主要消耗的资源</t>
+  </si>
+  <si>
     <t>最大物质量</t>
   </si>
   <si>
     <t>MaxMatter</t>
   </si>
   <si>
+    <t>物质量的上限</t>
+  </si>
+  <si>
     <t>物质回复率</t>
   </si>
   <si>
     <t>MatterRegenRate</t>
   </si>
   <si>
+    <t>物质每秒回复的数量</t>
+  </si>
+  <si>
     <t>物质消耗率</t>
   </si>
   <si>
     <t>MatterConsumeRate</t>
   </si>
   <si>
+    <t>物质每秒消耗的数量</t>
+  </si>
+  <si>
     <t>物质变化率</t>
   </si>
   <si>
     <t>MatterNetFlow</t>
+  </si>
+  <si>
+    <t>物质每秒变化的数量</t>
+  </si>
+  <si>
+    <t>(质能)转换率</t>
+  </si>
+  <si>
+    <t>ConversionRate</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>质能转换器转换物质/能量的产率</t>
+  </si>
+  <si>
+    <t>打印速度</t>
+  </si>
+  <si>
+    <t>PrintSpeed</t>
+  </si>
+  <si>
+    <t>质能打印机打印物品的速度（倍率）</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
+    <t>攻击造成暴击的几率</t>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
+    <t>暴击时的伤害倍率</t>
+  </si>
+  <si>
+    <t>WeaponCooldown</t>
+  </si>
+  <si>
+    <t>减少武器主动技能冷却时间的比例</t>
+  </si>
+  <si>
+    <t>模块冷却</t>
+  </si>
+  <si>
+    <t>ModuleCooldown</t>
+  </si>
+  <si>
+    <t>减少模块主动技能冷却时间的比例</t>
+  </si>
+  <si>
+    <t>PropUseSpeed</t>
+  </si>
+  <si>
+    <t>使用道具（有使用时间）时的速度</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>MovementSpeed</t>
+  </si>
+  <si>
+    <t>角色移动的速度</t>
+  </si>
+  <si>
+    <t>防具提供</t>
+  </si>
+  <si>
+    <t>物理抗性</t>
+  </si>
+  <si>
+    <t>PhysicalResistance</t>
+  </si>
+  <si>
+    <t>降低物理类型伤害的能力</t>
+  </si>
+  <si>
+    <t>能量抗性</t>
+  </si>
+  <si>
+    <t>EnergyResistance</t>
+  </si>
+  <si>
+    <t>降低能量类型伤害的能力</t>
+  </si>
+  <si>
+    <t>结构抗性</t>
+  </si>
+  <si>
+    <t>StructureResistance</t>
+  </si>
+  <si>
+    <t>降低结构类型伤害的能力</t>
   </si>
 </sst>
 </file>
@@ -327,7 +456,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +468,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -815,133 +952,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -958,7 +1095,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1620,7 +1757,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="14.6666666666667" defaultRowHeight="35" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="14.6666666666667" style="1" customWidth="1"/>
@@ -1652,7 +1789,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:6">
+    <row r="3" ht="28" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>63</v>
       </c>
@@ -1665,118 +1802,181 @@
       <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" ht="27" customHeight="1" spans="1:6">
-      <c r="A4" s="4"/>
+      <c r="E3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:6">
+      <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" ht="27" customHeight="1" spans="1:6">
-      <c r="A5" s="4"/>
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:6">
+      <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" ht="27" customHeight="1" spans="1:6">
-      <c r="A6" s="4"/>
+      <c r="E5" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:6">
+      <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" ht="27" customHeight="1" spans="1:6">
-      <c r="A7" s="4"/>
+      <c r="E6" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:6">
+      <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" ht="27" customHeight="1" spans="1:6">
+      <c r="E7" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="27" customHeight="1" spans="1:6">
-      <c r="A9" s="4"/>
+      <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:6">
+      <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" ht="27" customHeight="1" spans="1:6">
-      <c r="A10" s="4"/>
+      <c r="E9" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:6">
+      <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" ht="27" customHeight="1" spans="1:6">
-      <c r="A11" s="4"/>
+      <c r="E10" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:6">
+      <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" ht="27" customHeight="1" spans="1:6">
-      <c r="A12" s="4"/>
+      <c r="E11" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:6">
+      <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" ht="27" customHeight="1"/>
+      <c r="E12" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:6">
+      <c r="B13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:6">
+      <c r="B14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1"/>
+    <row r="16" ht="28" customHeight="1"/>
+    <row r="17" ht="28" customHeight="1"/>
+    <row r="18" ht="28" customHeight="1"/>
+    <row r="19" ht="28" customHeight="1"/>
+    <row r="20" ht="28" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
@@ -1793,10 +1993,205 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="15.2222222222222" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="15.2222222222222" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="54" customHeight="1" spans="1:6">
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1" spans="1:6">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1" spans="1:6">
+      <c r="B3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" spans="1:6">
+      <c r="B4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" ht="35" customHeight="1" spans="1:6">
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1" spans="1:6">
+      <c r="B6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1" spans="1:6">
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1" spans="1:6">
+      <c r="B8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1"/>
+    <row r="10" ht="27" customHeight="1"/>
+    <row r="11" ht="27" customHeight="1"/>
+    <row r="12" ht="27" customHeight="1" spans="1:6">
+      <c r="A12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1" spans="1:6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1"/>
+    <row r="16" ht="27" customHeight="1"/>
+    <row r="17" ht="27" customHeight="1"/>
+    <row r="18" ht="27" customHeight="1"/>
+    <row r="19" ht="27" customHeight="1"/>
+    <row r="20" ht="27" customHeight="1"/>
+    <row r="21" ht="27" customHeight="1"/>
+    <row r="22" ht="27" customHeight="1"/>
+    <row r="23" ht="27" customHeight="1"/>
+    <row r="24" ht="27" customHeight="1"/>
+    <row r="25" ht="27" customHeight="1"/>
+    <row r="26" ht="27" customHeight="1"/>
+    <row r="27" ht="27" customHeight="1"/>
+    <row r="28" ht="27" customHeight="1"/>
+    <row r="29" ht="27" customHeight="1"/>
+    <row r="30" ht="27" customHeight="1"/>
+    <row r="31" ht="27" customHeight="1"/>
+    <row r="32" ht="27" customHeight="1"/>
+    <row r="33" ht="27" customHeight="1"/>
+    <row r="34" ht="27" customHeight="1"/>
+    <row r="35" ht="27" customHeight="1"/>
+    <row r="36" ht="27" customHeight="1"/>
+    <row r="37" ht="27" customHeight="1"/>
+    <row r="38" ht="27" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A12:A14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>